--- a/Base_teste_iptu_2026.xlsx
+++ b/Base_teste_iptu_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Mauricio\Documents\portal-do-contribuinte\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B03CD2E7-9FDB-45CB-8150-D3A1B0ADF935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE3B67D-2960-4208-8E88-9B20317D1C77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6CCF0978-8E48-46CD-8FE9-B6D29E09E502}"/>
+    <workbookView xWindow="4110" yWindow="4110" windowWidth="21600" windowHeight="11295" xr2:uid="{6CCF0978-8E48-46CD-8FE9-B6D29E09E502}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
